--- a/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava est à la cuisine avec papa. Sur la table : une poire, une fraise, une cuillère, une fourchette. Papa dit : on nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Ava prend la poire. Elle prend la fraise. Elle les met dans le bol. C'est la catégorie des fruits. Elle prend la cuillère. Elle prend la fourchette. Elle les met dans le tiroir. C'est la catégorie des couverts. Papa dit : fruits ensemble. Couverts ensemble.</t>
+          <t>Ava est à la cuisine avec papa. Sur la table : une poire, une fraise, une cuillère, une fourchette. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Ava prend la poire. Elle prend la fraise. Elle les met dans le bol. C'est la catégorie des fruits. Elle prend la cuillère. Elle prend la fourchette. Elle les met dans le tiroir. C'est la catégorie des couverts. Fruits ensemble. Couverts ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ava est à la cuisine avec papa. Sur la table : une poire, une fraise, une cuillère, une fourchette.
+papa|On nomme. On classe.
+narrateur|Une catégorie pour les fruits. Une catégorie pour les couverts. Ava prend la poire. Elle prend la fraise. Elle les met dans le bol. C'est la catégorie des fruits. Elle prend la cuillère. Elle prend la fourchette. Elle les met dans le tiroir. C'est la catégorie des couverts.
+papa|Fruits ensemble. Couverts ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ava range poire et cuillère. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a classé. Une catégorie pour les fruits. Une catégorie pour les couverts.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ava croque la poire. Papa range le tiroir.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 papa|Fruits ensemble. Couverts ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Ava range poire et cuillère. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Ava a classé. Une catégorie pour les fruits. Une catégorie pour les couverts.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Ava croque la poire. Papa range le tiroir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ava classe fruits et couverts</t>
+          <t>La buée et les deux tas de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la soupe, la table de Mila est encore chaude. Poires et fraises d'un côté, couverts de l'autre. Elle nomme et classe deux catégories.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava est à la cuisine avec papa. Sur la table : une poire, une fraise, une cuillère, une fourchette. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Ava prend la poire. Elle prend la fraise. Elle les met dans le bol. C'est la catégorie des fruits. Elle prend la cuillère. Elle prend la fourchette. Elle les met dans le tiroir. C'est la catégorie des couverts. Fruits ensemble. Couverts ensemble.</t>
+          <t>De la buée dessine des ronds sur la vitre. La soupe sent encore le poireau. Une cuillère frappe le bord du bol. Des chaussures mouillées sèchent près de la porte. Le bois de la table est encore tiède. Un tiroir grince, tout bas. Mila, tu as vu les ronds dans la buée ? Oui, papa. On dirait des bulles. La soupe est finie. La table a encore des choses dessus. En ce moment, Mila s'approche de la table. Sur la table : une poire. Une fraise. Une cuillère. Une fourchette. La poire est lisse. La fraise est un peu sucrée, déjà. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Mila prend la poire verte. Elle est froide dans la paume. Poire. C'est un fruit. Mets-la dans le bol. Mila pose la poire dans le bol. Le bol fait un petit bruit sourd. Elle prend la fraise rouge. Les petits grains piquent un peu le doigt. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Mila met la fraise avec la poire. Elle prend la cuillère. Le métal est froid et lisse. Cuillère. C'est un couvert. Oui. Le tiroir est ouvert, tout près. Mila glisse la cuillère dans le tiroir. Elle prend la fourchette. Les dents brillent un peu. Fourchette. C'est un couvert. Les couverts ensemble. C'est une catégorie. Mila met la fourchette avec la cuillère. Le tiroir se ferme, tout doux. Catégorie. Fruits. Couverts. Bravo, Mila. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger la table ? Oui, maman. Le bol a les fruits. Le tiroir a les couverts. La buée commence à descendre sur la vitre. On entend encore la rue, tout loin. Et les chaussures sèchent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ava est à la cuisine avec papa. Sur la table : une poire, une fraise, une cuillère, une fourchette.
-papa|On nomme. On classe.
-narrateur|Une catégorie pour les fruits. Une catégorie pour les couverts. Ava prend la poire. Elle prend la fraise. Elle les met dans le bol. C'est la catégorie des fruits. Elle prend la cuillère. Elle prend la fourchette. Elle les met dans le tiroir. C'est la catégorie des couverts.
-papa|Fruits ensemble. Couverts ensemble.</t>
+          <t>narrateur|De la buée dessine des ronds sur la vitre.
+narrateur|La soupe sent encore le poireau.
+narrateur|Une cuillère frappe le bord du bol.
+narrateur|Des chaussures mouillées sèchent près de la porte.
+narrateur|Le bois de la table est encore tiède.
+narrateur|Un tiroir grince, tout bas.
+papa|Mila, tu as vu les ronds dans la buée ?
+enfant-f|Oui, papa.
+enfant-f|On dirait des bulles.
+maman|La soupe est finie.
+maman|La table a encore des choses dessus.
+narrateur|En ce moment, Mila s'approche de la table.
+narrateur|Sur la table : une poire.
+narrateur|Une fraise.
+narrateur|Une cuillère.
+narrateur|Une fourchette.
+enfant-f|La poire est lisse.
+enfant-f|La fraise est un peu sucrée, déjà.
+papa|On nomme.
+papa|On classe.
+papa|Une catégorie pour les fruits.
+papa|Une catégorie pour les couverts.
+narrateur|Mila prend la poire verte.
+narrateur|Elle est froide dans la paume.
+enfant-f|Poire.
+enfant-f|C'est un fruit.
+papa|Mets-la dans le bol.
+narrateur|Mila pose la poire dans le bol.
+narrateur|Le bol fait un petit bruit sourd.
+narrateur|Elle prend la fraise rouge.
+narrateur|Les petits grains piquent un peu le doigt.
+enfant-f|Fraise.
+enfant-f|C'est un fruit aussi.
+maman|Les fruits ensemble.
+maman|C'est une catégorie.
+narrateur|Mila met la fraise avec la poire.
+narrateur|Elle prend la cuillère.
+narrateur|Le métal est froid et lisse.
+enfant-f|Cuillère.
+enfant-f|C'est un couvert.
+papa|Oui.
+papa|Le tiroir est ouvert, tout près.
+narrateur|Mila glisse la cuillère dans le tiroir.
+narrateur|Elle prend la fourchette.
+narrateur|Les dents brillent un peu.
+enfant-f|Fourchette.
+enfant-f|C'est un couvert.
+papa|Les couverts ensemble.
+papa|C'est une catégorie.
+narrateur|Mila met la fourchette avec la cuillère.
+narrateur|Le tiroir se ferme, tout doux.
+enfant-f|Catégorie.
+enfant-f|Fruits.
+enfant-f|Couverts.
+papa|Bravo, Mila.
+papa|Tu as nommé.
+papa|Tu as classé.
+papa|Tu as mis ensemble.
+maman|C'est du bon travail.
+maman|Tu as fini de ranger la table ?
+enfant-f|Oui, maman.
+narrateur|Le bol a les fruits.
+narrateur|Le tiroir a les couverts.
+narrateur|La buée commence à descendre sur la vitre.
+papa|On entend encore la rue, tout loin.
+enfant-f|Et les chaussures sèchent.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1343,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ava range poire et cuillère. Que fait-elle ?</t>
+          <t>Mila range poire et cuillère. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ava range poire et cuillère. Que fait-elle ?</t>
+          <t>narrateur|Mila range poire et cuillère.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ava a classé. Une catégorie pour les fruits. Une catégorie pour les couverts.</t>
+          <t>Mila a classé. Une catégorie pour les fruits. Une catégorie pour les couverts. Tu as mis ensemble. Bravo. C'est du bon travail, Mila. Le bol est prêt ? Oui. Les fruits sont ensemble. Et les couverts ? Dans le tiroir. La table est plus claire, maintenant. Il reste un rond de buée, tout petit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1746,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ava a classé. Une catégorie pour les fruits. Une catégorie pour les couverts.</t>
+          <t>narrateur|Mila a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les couverts.
+papa|Tu as mis ensemble.
+papa|Bravo.
+maman|C'est du bon travail, Mila.
+maman|Le bol est prêt ?
+enfant-f|Oui.
+enfant-f|Les fruits sont ensemble.
+papa|Et les couverts ?
+enfant-f|Dans le tiroir.
+narrateur|La table est plus claire, maintenant.
+narrateur|Il reste un rond de buée, tout petit.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ava croque la poire. Papa range le tiroir.</t>
+          <t>Mila croque la poire. Elle est juteuse, un peu ferme. Tu aimes le croquant ? Oui, papa. Papa range le tiroir jusqu'au bout. La cuillère et la fourchette sont côte à côte. On garde la fraise pour tout à l'heure ? Oui, maman. Elle reste dans le bol. Les fruits ensemble. Les couverts ensemble. Les chaussures mouillées ont presque séché. La vitre est plus claire. Tu as classé, puis tu croques. C'était un bon jeu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1835,7 +1922,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ava croque la poire. Papa range le tiroir.</t>
+          <t>narrateur|Mila croque la poire.
+narrateur|Elle est juteuse, un peu ferme.
+papa|Tu aimes le croquant ?
+enfant-f|Oui, papa.
+narrateur|Papa range le tiroir jusqu'au bout.
+narrateur|La cuillère et la fourchette sont côte à côte.
+maman|On garde la fraise pour tout à l'heure ?
+enfant-f|Oui, maman.
+enfant-f|Elle reste dans le bol.
+maman|Les fruits ensemble.
+papa|Les couverts ensemble.
+narrateur|Les chaussures mouillées ont presque séché.
+narrateur|La vitre est plus claire.
+papa|Tu as classé, puis tu croques.
+enfant-f|C'était un bon jeu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1863,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai classé. Fruits. Couverts. Bravo. Tu as fait du bon travail. Deux catégories, bien rangées. La buée a quitté la vitre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2003,7 +2104,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai classé.
+enfant-f|Fruits.
+enfant-f|Couverts.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Deux catégories, bien rangées.
+narrateur|La buée a quitté la vitre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2025,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la buée dessine des ronds sur la vitre. La soupe sent encore le poireau. Une cuillère frappe le bord du bol. Des chaussures mouillées sèchent près de la porte. Le bois de la table est encore tiède. Un tiroir grince, tout bas. Mila, tu as vu les ronds dans la buée ? Oui, papa. On dirait des bulles. La soupe est finie. La table a encore des choses dessus. En ce moment, Mila s'approche de la table. Sur la table : une poire. Une fraise. Une cuillère. Une fourchette. La poire est lisse. La fraise est un peu sucrée, déjà. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Mila prend la poire verte. Elle est froide dans la paume. Poire. C'est un fruit. Mets-la dans le bol. Mila pose la poire dans le bol. Le bol fait un petit bruit sourd. Elle prend la fraise rouge. Les petits grains piquent un peu le doigt. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Mila met la fraise avec la poire. Elle prend la cuillère. Le métal est froid et lisse. Cuillère. C'est un couvert. Oui. Le tiroir est ouvert, tout près. Mila glisse la cuillère dans le tiroir. Elle prend la fourchette. Les dents brillent un peu. Fourchette. C'est un couvert. Les couverts ensemble. C'est une catégorie. Mila met la fourchette avec la cuillère. Le tiroir se ferme, tout doux. Catégorie. Fruits. Couverts. Bravo, Mila. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger la table ? Oui, maman. Le bol a les fruits. Le tiroir a les couverts. La buée commence à descendre sur la vitre. On entend encore la rue, tout loin. Et les chaussures sèchent.</t>
+          <t>De la buée dessine des ronds sur la vitre. La soupe sent encore le poireau. Une cuillère frappe le bord du bol. Des chaussures mouillées sèchent près de la porte. Le bois de la table est encore tiède. Un tiroir grince, tout bas. Mila, tu as vu les ronds dans la buée ? Oui, papa. On dirait des bulles. La soupe est finie. La table a encore des choses dessus. En ce moment, Mila s'approche de la table. Sur la table : une poire. Une fraise. Une cuillère. Une fourchette. La poire est lisse. La fraise est un peu sucrée, déjà. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Mila prend la poire verte. Elle est froide dans la paume. Poire. C'est un fruit. Mets-la dans le bol. Mila pose la poire dans le bol. Le bol fait un petit bruit sourd. Elle prend la fraise rouge. Les petits grains piquent un peu le doigt. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Mila met la fraise avec la poire. Elle prend la cuillère. Le métal est froid et lisse. Cuillère. C'est un couvert. Oui. Le tiroir est ouvert, tout près. Mila glisse la cuillère dans le tiroir. Elle prend la fourchette. Les dents brillent un peu. Fourchette. C'est un couvert. Les couverts ensemble. C'est une catégorie. Mila met la fourchette avec la cuillère. Le tiroir se ferme, tout doux. Catégorie. Fruits. Couverts. Bravo, Mila. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger la table ? Oui, maman. Le bol a les fruits. Le tiroir a les couverts. La buée commence à descendre sur la vitre. On entend encore la rue, tout loin. Et les chaussures sèchent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava est à la cuisine avec papa. Sur la table : une poire, une fraise, une cuillère, une fourchette. Papa dit : on nomme. On classe. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les couverts. Ava prend la poire. Elle prend la fraise. Elle les met dans le bol. C'est la catégorie des fruits. Elle prend la cuillère. Elle prend la fourchette. Elle les met dans le tiroir. C'est la catégorie des couverts. Papa dit : fruits ensemble. Couverts ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>De la buée dessine des ronds sur la vitre. La soupe sent encore le poireau. Une cuillère frappe le bord du bol. Des chaussures mouillées sèchent près de la porte. Le bois de la table est encore tiède. Un tiroir grince, tout bas. Mila, tu as vu les ronds dans la buée ? Oui, papa. On dirait des bulles. La soupe est finie. La table a encore des choses dessus. En ce moment, Mila s'approche de la table. Sur la table : une poire. Une fraise. Une cuillère. Une fourchette. La poire est lisse. La fraise est un peu sucrée, déjà. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les couverts. Mila prend la poire verte. Elle est froide dans la paume. Poire. C'est un fruit. Mets-la dans le bol. Mila pose la poire dans le bol. Le bol fait un petit bruit sourd. Elle prend la fraise rouge. Les petits grains piquent un peu le doigt. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Mila met la fraise avec la poire. Elle prend la cuillère. Le métal est froid et lisse. Cuillère. C'est un couvert. Oui. Le tiroir est ouvert, tout près. Mila glisse la cuillère dans le tiroir. Elle prend la fourchette. Les dents brillent un peu. Fourchette. C'est un couvert. Les couverts ensemble. C'est une catégorie. Mila met la fourchette avec la cuillère. Le tiroir se ferme, tout doux. Catégorie. Fruits. Couverts. Bravo, Mila. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger la table ? Oui, maman. Le bol a les fruits. Le tiroir a les couverts. La buée commence à descendre sur la vitre. On entend encore la rue, tout loin. Et les chaussures sèchent.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1382,7 +1382,6 @@
 papa|Tu as nommé.
 papa|Tu as classé.
 papa|Tu as mis ensemble.
-maman|C'est du bon travail.
 maman|Tu as fini de ranger la table ?
 enfant-f|Oui, maman.
 narrateur|Le bol a les fruits.
@@ -1392,7 +1391,6 @@
 enfant-f|Et les chaussures sèchent.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1422,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ava range poire et cuillère. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila range poire et cuillère. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1575,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a classé. Une catégorie pour les fruits. Une catégorie pour les couverts. Tu as mis ensemble. Bravo. C'est du bon travail, Mila. Le bol est prêt ? Oui. Les fruits sont ensemble. Et les couverts ? Dans le tiroir. La table est plus claire, maintenant. Il reste un rond de buée, tout petit.</t>
+          <t>Mila a classé. Une catégorie pour les fruits. Une catégorie pour les couverts. Tu as mis ensemble. Bravo. Le bol est prêt ? Oui. Les fruits sont ensemble. Et les couverts ? Dans le tiroir. La table est plus claire, maintenant. Il reste un rond de buée, tout petit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les couverts.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a classé. Une catégorie pour les fruits. Une catégorie pour les couverts. Tu as mis ensemble. Bravo. Le bol est prêt ? Oui. Les fruits sont ensemble. Et les couverts ? Dans le tiroir. La table est plus claire, maintenant. Il reste un rond de buée, tout petit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1748,6 @@
 narrateur|Une catégorie pour les couverts.
 papa|Tu as mis ensemble.
 papa|Bravo.
-maman|C'est du bon travail, Mila.
 maman|Le bol est prêt ?
 enfant-f|Oui.
 enfant-f|Les fruits sont ensemble.
@@ -1761,7 +1757,6 @@
 narrateur|Il reste un rond de buée, tout petit.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ava croque la poire. Papa range le tiroir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila croque la poire. Elle est juteuse, un peu ferme. Tu aimes le croquant ? Oui, papa. Papa range le tiroir jusqu'au bout. La cuillère et la fourchette sont côte à côte. On garde la fraise pour tout à l'heure ? Oui, maman. Elle reste dans le bol. Les fruits ensemble. Les couverts ensemble. Les chaussures mouillées ont presque séché. La vitre est plus claire. Tu as classé, puis tu croques. C'était un bon jeu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1934,6 @@
 enfant-f|C'était un bon jeu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai classé. Fruits. Couverts. Bravo. Tu as fait du bon travail. Deux catégories, bien rangées. La buée a quitté la vitre. L'histoire est finie.</t>
+          <t>J'ai classé. Fruits. Couverts. Bravo. Deux catégories, bien rangées. La buée a quitté la vitre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai classé. Fruits. Couverts. Bravo. Deux catégories, bien rangées. La buée a quitté la vitre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,13 +2102,10 @@
 enfant-f|Fruits.
 enfant-f|Couverts.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 maman|Deux catégories, bien rangées.
-narrateur|La buée a quitté la vitre.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La buée a quitté la vitre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ava, papa</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
